--- a/outputs/06_测试数据/发动机主线业务流程-多工厂一级工艺版/导入包/生产订单_模板.xlsx
+++ b/outputs/06_测试数据/发动机主线业务流程-多工厂一级工艺版/导入包/生产订单_模板.xlsx
@@ -912,14 +912,22 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Mat002</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="8" t="inlineStr"/>
+          <t>MAT-ENG-001</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>A.01</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>MBOM-ENG-A1000-V1</t>
+        </is>
+      </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>AE-100-002</t>
+          <t>A1000</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
@@ -929,7 +937,7 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Rt010</t>
+          <t>RT-L1-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
@@ -938,10 +946,10 @@
         </is>
       </c>
       <c r="J2" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K2" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L2" s="8" t="n">
         <v>0</v>
@@ -954,40 +962,40 @@
       </c>
       <c r="O2" s="8" t="inlineStr">
         <is>
-          <t>2025-03-01 08:00:00</t>
+          <t>2026-06-03 09:00:00</t>
         </is>
       </c>
       <c r="P2" s="8" t="inlineStr">
         <is>
-          <t>2025-03-02 08:00:00</t>
+          <t>2026-06-20 18:00:00</t>
         </is>
       </c>
       <c r="Q2" s="8" t="inlineStr">
         <is>
-          <t>零部件加工计划</t>
+          <t>零部件生产计划</t>
         </is>
       </c>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="8" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>零部件生产已排产</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="8" t="inlineStr">
         <is>
-          <t>初始</t>
+          <t>已展开</t>
         </is>
       </c>
       <c r="V2" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W2" s="8" t="inlineStr"/>
       <c r="X2" s="8" t="inlineStr"/>
       <c r="Y2" s="8" t="inlineStr"/>
       <c r="Z2" s="8" t="inlineStr">
         <is>
-          <t>K2002</t>
+          <t>liumin</t>
         </is>
       </c>
       <c r="AA2" s="8" t="inlineStr">
@@ -1005,7 +1013,7 @@
       <c r="AE2" s="8" t="inlineStr"/>
       <c r="AF2" s="8" t="inlineStr">
         <is>
-          <t>Biz010</t>
+          <t>ORG-PD-001</t>
         </is>
       </c>
       <c r="AG2" s="8" t="inlineStr"/>
@@ -1029,12 +1037,12 @@
       <c r="AY2" s="8" t="inlineStr"/>
       <c r="AZ2" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-001</t>
+          <t>PO-ENG-A1000-20260603-0001</t>
         </is>
       </c>
       <c r="BA2" s="8" t="inlineStr">
         <is>
-          <t>机匣机加完件生产订单，按10-机加厂正式工艺组织执行</t>
+          <t>厂际协同计划父生产订单，对应 E2E-MOM-ENG-001。</t>
         </is>
       </c>
       <c r="BB2" s="8" t="inlineStr">
@@ -1049,12 +1057,12 @@
       </c>
       <c r="BD2" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-001</t>
+          <t>PO-ENG-A1000-20260603-0001</t>
         </is>
       </c>
       <c r="BE2" s="8" t="inlineStr">
         <is>
-          <t>2025-03-01 04:00:00</t>
+          <t>2026-06-03 08:30:00</t>
         </is>
       </c>
     </row>
@@ -1071,14 +1079,14 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Mat004</t>
+          <t>MAT-CAS-001</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr"/>
       <c r="E3" s="8" t="inlineStr"/>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>AE-100-004</t>
+          <t>A1000</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -1088,7 +1096,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Rt020</t>
+          <t>RT-MC-CAS-A1000-V1</t>
         </is>
       </c>
       <c r="I3" s="8" t="inlineStr">
@@ -1097,10 +1105,10 @@
         </is>
       </c>
       <c r="J3" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K3" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L3" s="8" t="n">
         <v>0</v>
@@ -1113,12 +1121,12 @@
       </c>
       <c r="O3" s="8" t="inlineStr">
         <is>
-          <t>2025-03-03 08:00:00</t>
+          <t>2026-06-03 10:00:00</t>
         </is>
       </c>
       <c r="P3" s="8" t="inlineStr">
         <is>
-          <t>2025-03-04 08:00:00</t>
+          <t>2026-06-11 18:00:00</t>
         </is>
       </c>
       <c r="Q3" s="8" t="inlineStr">
@@ -1139,14 +1147,14 @@
         </is>
       </c>
       <c r="V3" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W3" s="8" t="inlineStr"/>
       <c r="X3" s="8" t="inlineStr"/>
       <c r="Y3" s="8" t="inlineStr"/>
       <c r="Z3" s="8" t="inlineStr">
         <is>
-          <t>K2002</t>
+          <t>liumin</t>
         </is>
       </c>
       <c r="AA3" s="8" t="inlineStr">
@@ -1164,7 +1172,7 @@
       <c r="AE3" s="8" t="inlineStr"/>
       <c r="AF3" s="8" t="inlineStr">
         <is>
-          <t>Biz020</t>
+          <t>ORG-MC-001</t>
         </is>
       </c>
       <c r="AG3" s="8" t="inlineStr"/>
@@ -1188,12 +1196,12 @@
       <c r="AY3" s="8" t="inlineStr"/>
       <c r="AZ3" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-002</t>
+          <t>PO-ENG-A1000-20260603-0001-001</t>
         </is>
       </c>
       <c r="BA3" s="8" t="inlineStr">
         <is>
-          <t>盘轴模块生产订单，按20-盘轴厂正式工艺组织执行</t>
+          <t>10-机加厂子生产订单。</t>
         </is>
       </c>
       <c r="BB3" s="8" t="inlineStr">
@@ -1208,12 +1216,12 @@
       </c>
       <c r="BD3" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-002</t>
+          <t>PO-ENG-A1000-20260603-0001-001</t>
         </is>
       </c>
       <c r="BE3" s="8" t="inlineStr">
         <is>
-          <t>2025-03-03 04:00:00</t>
+          <t>2026-06-03 09:00:00</t>
         </is>
       </c>
     </row>
@@ -1230,14 +1238,14 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Mat006</t>
+          <t>MAT-SHAFT-001</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr"/>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>AE-100-006</t>
+          <t>A1000</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1247,7 +1255,7 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Rt030</t>
+          <t>RT-SH-SHAFT-A1000-V1</t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
@@ -1256,10 +1264,10 @@
         </is>
       </c>
       <c r="J4" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K4" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L4" s="8" t="n">
         <v>0</v>
@@ -1272,12 +1280,12 @@
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
-          <t>2025-03-05 08:00:00</t>
+          <t>2026-06-03 10:00:00</t>
         </is>
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>2026-06-12 18:00:00</t>
         </is>
       </c>
       <c r="Q4" s="8" t="inlineStr">
@@ -1298,14 +1306,14 @@
         </is>
       </c>
       <c r="V4" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W4" s="8" t="inlineStr"/>
       <c r="X4" s="8" t="inlineStr"/>
       <c r="Y4" s="8" t="inlineStr"/>
       <c r="Z4" s="8" t="inlineStr">
         <is>
-          <t>K2002</t>
+          <t>liumin</t>
         </is>
       </c>
       <c r="AA4" s="8" t="inlineStr">
@@ -1323,7 +1331,7 @@
       <c r="AE4" s="8" t="inlineStr"/>
       <c r="AF4" s="8" t="inlineStr">
         <is>
-          <t>Biz030</t>
+          <t>ORG-SH-001</t>
         </is>
       </c>
       <c r="AG4" s="8" t="inlineStr"/>
@@ -1347,12 +1355,12 @@
       <c r="AY4" s="8" t="inlineStr"/>
       <c r="AZ4" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-003</t>
+          <t>PO-ENG-A1000-20260603-0001-002</t>
         </is>
       </c>
       <c r="BA4" s="8" t="inlineStr">
         <is>
-          <t>叶片组件生产订单，按30-叶片厂正式工艺组织执行</t>
+          <t>20-盘轴厂子生产订单。</t>
         </is>
       </c>
       <c r="BB4" s="8" t="inlineStr">
@@ -1367,12 +1375,12 @@
       </c>
       <c r="BD4" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-003</t>
+          <t>PO-ENG-A1000-20260603-0001-002</t>
         </is>
       </c>
       <c r="BE4" s="8" t="inlineStr">
         <is>
-          <t>2025-03-05 04:00:00</t>
+          <t>2026-06-03 09:05:00</t>
         </is>
       </c>
     </row>
@@ -1389,14 +1397,14 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Mat011</t>
+          <t>MAT-BLADESET-001</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>AE-100</t>
+          <t>A1000</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -1406,7 +1414,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Rt040</t>
+          <t>RT-BL-BLADESET-A1000-V1</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
@@ -1415,10 +1423,10 @@
         </is>
       </c>
       <c r="J5" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K5" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L5" s="8" t="n">
         <v>0</v>
@@ -1431,12 +1439,12 @@
       </c>
       <c r="O5" s="8" t="inlineStr">
         <is>
-          <t>2025-03-07 08:00:00</t>
+          <t>2026-06-03 10:00:00</t>
         </is>
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
-          <t>2025-03-08 02:00:00</t>
+          <t>2026-06-13 18:00:00</t>
         </is>
       </c>
       <c r="Q5" s="8" t="inlineStr">
@@ -1464,7 +1472,7 @@
       <c r="Y5" s="8" t="inlineStr"/>
       <c r="Z5" s="8" t="inlineStr">
         <is>
-          <t>K2002</t>
+          <t>liumin</t>
         </is>
       </c>
       <c r="AA5" s="8" t="inlineStr">
@@ -1482,7 +1490,7 @@
       <c r="AE5" s="8" t="inlineStr"/>
       <c r="AF5" s="8" t="inlineStr">
         <is>
-          <t>Biz040</t>
+          <t>ORG-BL-001</t>
         </is>
       </c>
       <c r="AG5" s="8" t="inlineStr"/>
@@ -1506,12 +1514,12 @@
       <c r="AY5" s="8" t="inlineStr"/>
       <c r="AZ5" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-004</t>
+          <t>PO-ENG-A1000-20260603-0001-003</t>
         </is>
       </c>
       <c r="BA5" s="8" t="inlineStr">
         <is>
-          <t>航空发动机总成生产订单，按40-装配厂正式工艺组织执行</t>
+          <t>30-叶片厂子生产订单。</t>
         </is>
       </c>
       <c r="BB5" s="8" t="inlineStr">
@@ -1526,12 +1534,12 @@
       </c>
       <c r="BD5" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-004</t>
+          <t>PO-ENG-A1000-20260603-0001-003</t>
         </is>
       </c>
       <c r="BE5" s="8" t="inlineStr">
         <is>
-          <t>2025-03-07 04:00:00</t>
+          <t>2026-06-03 09:10:00</t>
         </is>
       </c>
     </row>
@@ -1548,14 +1556,22 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Mat011</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
+          <t>MAT-ENG-001</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>A.01</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>MBOM-ENG-A1000-V1</t>
+        </is>
+      </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>AE-100</t>
+          <t>A1000</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1565,7 +1581,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Rt900</t>
+          <t>RT-ASM-ENG-A1000-V1</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -1574,10 +1590,10 @@
         </is>
       </c>
       <c r="J6" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L6" s="8" t="n">
         <v>0</v>
@@ -1590,23 +1606,23 @@
       </c>
       <c r="O6" s="8" t="inlineStr">
         <is>
-          <t>2025-03-09 08:00:00</t>
+          <t>2026-06-13 08:30:00</t>
         </is>
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>2025-03-10 00:00:00</t>
+          <t>2026-06-20 18:00:00</t>
         </is>
       </c>
       <c r="Q6" s="8" t="inlineStr">
         <is>
-          <t>零部件生产计划</t>
+          <t>零部件加工计划</t>
         </is>
       </c>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="8" t="inlineStr">
         <is>
-          <t>零部件生产已排产</t>
+          <t>无</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr"/>
@@ -1623,7 +1639,7 @@
       <c r="Y6" s="8" t="inlineStr"/>
       <c r="Z6" s="8" t="inlineStr">
         <is>
-          <t>K2002</t>
+          <t>liumin</t>
         </is>
       </c>
       <c r="AA6" s="8" t="inlineStr">
@@ -1641,7 +1657,7 @@
       <c r="AE6" s="8" t="inlineStr"/>
       <c r="AF6" s="8" t="inlineStr">
         <is>
-          <t>Biz900</t>
+          <t>ORG-AS-001</t>
         </is>
       </c>
       <c r="AG6" s="8" t="inlineStr"/>
@@ -1665,12 +1681,12 @@
       <c r="AY6" s="8" t="inlineStr"/>
       <c r="AZ6" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-005</t>
+          <t>PO-ENG-A1000-20260603-0001-004</t>
         </is>
       </c>
       <c r="BA6" s="8" t="inlineStr">
         <is>
-          <t>航空发动机总成生产订单，按发动机一级协同工艺组织执行</t>
+          <t>40-装配厂子生产订单，释放数量与释放状态由后续业务动作驱动。</t>
         </is>
       </c>
       <c r="BB6" s="8" t="inlineStr">
@@ -1685,12 +1701,12 @@
       </c>
       <c r="BD6" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-005</t>
+          <t>PO-ENG-A1000-20260603-0001-004</t>
         </is>
       </c>
       <c r="BE6" s="8" t="inlineStr">
         <is>
-          <t>2025-03-09 04:00:00</t>
+          <t>2026-06-03 09:15:00</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7425,7 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-001</t>
+          <t>PO-ENG-A1000-20260603-0001-001</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
@@ -7419,16 +7435,16 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Mat001</t>
+          <t>MAT-CAS-BLANK-001</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>机匣毛坯上线与找正</t>
+          <t>机匣粗加工</t>
         </is>
       </c>
       <c r="E2" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F2" s="8" t="n">
         <v>1</v>
@@ -7442,14 +7458,14 @@
       </c>
       <c r="J2" s="8" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-002</t>
+          <t>PO-ENG-A1000-20260603-0001-002</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -7459,16 +7475,16 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Mat003</t>
+          <t>MAT-SHAFT-BLANK-001</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>盘轴复合加工</t>
+          <t>盘轴加工</t>
         </is>
       </c>
       <c r="E3" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F3" s="8" t="n">
         <v>1</v>
@@ -7482,14 +7498,14 @@
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-003</t>
+          <t>PO-ENG-A1000-20260603-0001-003</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -7499,16 +7515,16 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Mat005</t>
+          <t>MAT-BLADE-BLANK-001</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>叶片成型加工</t>
+          <t>叶片成型</t>
         </is>
       </c>
       <c r="E4" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F4" s="8" t="n">
         <v>1</v>
@@ -7522,14 +7538,14 @@
       </c>
       <c r="J4" s="8" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-003</t>
+          <t>PO-ENG-A1000-20260603-0001-004</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -7539,16 +7555,16 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Mat009</t>
+          <t>MAT-CAS-001</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>叶片表面涂层处理</t>
+          <t>装配准备</t>
         </is>
       </c>
       <c r="E5" s="8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>1</v>
@@ -7562,14 +7578,14 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>0020</t>
+          <t>OP10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-004</t>
+          <t>PO-ENG-A1000-20260603-0001-004</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -7579,16 +7595,16 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Mat002</t>
+          <t>MAT-SHAFT-001</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>齐套确认</t>
+          <t>装配准备</t>
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>1</v>
@@ -7602,14 +7618,14 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>MO-ENG20S01-004</t>
+          <t>PO-ENG-A1000-20260603-0001-004</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -7619,16 +7635,16 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Mat004</t>
+          <t>MAT-BLADESET-001</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>齐套确认</t>
+          <t>装配准备</t>
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>1</v>
@@ -7642,209 +7658,69 @@
       </c>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>0010</t>
+          <t>OP10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>MO-ENG20S01-004</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Mat006</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>齐套确认</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>12</v>
-      </c>
+      <c r="A8" s="8" t="inlineStr"/>
+      <c r="B8" s="8" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr"/>
       <c r="G8" s="8" t="inlineStr"/>
       <c r="H8" s="8" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>0010</t>
-        </is>
-      </c>
+      <c r="I8" s="8" t="inlineStr"/>
+      <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>MO-ENG20S01-004</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Mat007</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>齐套确认</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="A9" s="8" t="inlineStr"/>
+      <c r="B9" s="8" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr"/>
       <c r="H9" s="8" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>0010</t>
-        </is>
-      </c>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>MO-ENG20S01-004</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Mat008</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>齐套确认</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="A10" s="8" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
       <c r="G10" s="8" t="inlineStr"/>
       <c r="H10" s="8" t="inlineStr"/>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>0010</t>
-        </is>
-      </c>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>MO-ENG20S01-004</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Mat010</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>整机试车与交付放行</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="A11" s="8" t="inlineStr"/>
+      <c r="B11" s="8" t="inlineStr"/>
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr"/>
       <c r="G11" s="8" t="inlineStr"/>
       <c r="H11" s="8" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>0030</t>
-        </is>
-      </c>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>MO-ENG20S01-004</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>A.01</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Mat012</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>整机试车与交付放行</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>1</v>
-      </c>
+      <c r="A12" s="8" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
       <c r="G12" s="8" t="inlineStr"/>
       <c r="H12" s="8" t="inlineStr"/>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>0030</t>
-        </is>
-      </c>
+      <c r="I12" s="8" t="inlineStr"/>
+      <c r="J12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr"/>
